--- a/3_CGE/Game_theory_2024/0_External_data/qo_values.xlsx
+++ b/3_CGE/Game_theory_2024/0_External_data/qo_values.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\runGTAP375\Game_theory_2024\0_External_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB5DE93-095D-407E-BF5C-D8258C690B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF9EA09-B3E2-49C9-BEAA-FAB0E4F31285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10960" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{43EE81B5-F536-4A52-A633-6CC0AA8FC546}"/>
+    <workbookView xWindow="16690" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{43EE81B5-F536-4A52-A633-6CC0AA8FC546}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Country</t>
   </si>
@@ -56,9 +59,6 @@
     <t xml:space="preserve">colombia   </t>
   </si>
   <si>
-    <t xml:space="preserve">angdrc     </t>
-  </si>
-  <si>
     <t xml:space="preserve">ghana      </t>
   </si>
   <si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>wht</t>
+  </si>
+  <si>
+    <t>angola</t>
+  </si>
+  <si>
+    <t>drc</t>
   </si>
 </sst>
 </file>
@@ -164,10 +170,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -183,6 +190,360 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Additional_LU_and_deforestation"/>
+      <sheetName val="Land_Cover"/>
+      <sheetName val="Land_Cover_MIN_MAX"/>
+      <sheetName val="GTAP_area"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Shocks_GlobalTarf_qxw"/>
+      <sheetName val="Shocks_tmf_f"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Shocks_tmf_f2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="21">
+          <cell r="BM21">
+            <v>3.2592816165294627</v>
+          </cell>
+          <cell r="BN21">
+            <v>10.33368572011617</v>
+          </cell>
+          <cell r="BO21">
+            <v>22.394819271147433</v>
+          </cell>
+          <cell r="BP21">
+            <v>3.5330811594172671</v>
+          </cell>
+          <cell r="BQ21">
+            <v>2.0125972621416643</v>
+          </cell>
+          <cell r="BR21">
+            <v>4.4628622369061421</v>
+          </cell>
+          <cell r="BS21">
+            <v>1.6687258339981561</v>
+          </cell>
+          <cell r="BT21">
+            <v>2.7598774804851423</v>
+          </cell>
+          <cell r="BU21">
+            <v>1.0050811425673827</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="BM59">
+            <v>12.649951689465617</v>
+          </cell>
+          <cell r="BN59">
+            <v>2.576452136380186</v>
+          </cell>
+          <cell r="BO59">
+            <v>28.273817766748337</v>
+          </cell>
+          <cell r="BP59">
+            <v>11.385096173096438</v>
+          </cell>
+          <cell r="BQ59">
+            <v>13.405632030785759</v>
+          </cell>
+          <cell r="BR59">
+            <v>8.534651666069939</v>
+          </cell>
+          <cell r="BS59">
+            <v>36.361072353619136</v>
+          </cell>
+          <cell r="BT59">
+            <v>5.1946086854736313</v>
+          </cell>
+          <cell r="BU59">
+            <v>30.704496097842831</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="BM78">
+            <v>1.6723376794962399</v>
+          </cell>
+          <cell r="BN78">
+            <v>1.9196079004924875</v>
+          </cell>
+          <cell r="BO78">
+            <v>2.7558985848572726</v>
+          </cell>
+          <cell r="BP78">
+            <v>0.1604641310330728</v>
+          </cell>
+          <cell r="BQ78">
+            <v>4.1152896617819481</v>
+          </cell>
+          <cell r="BR78">
+            <v>0.32415605702635442</v>
+          </cell>
+          <cell r="BS78">
+            <v>5.2871023596143258</v>
+          </cell>
+          <cell r="BT78">
+            <v>0.4551162969937726</v>
+          </cell>
+          <cell r="BU78">
+            <v>4.3082198150677886</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="BM97">
+            <v>5.8083733799160093</v>
+          </cell>
+          <cell r="BN97">
+            <v>1.8673556284186359</v>
+          </cell>
+          <cell r="BO97">
+            <v>6.5249602147018653</v>
+          </cell>
+          <cell r="BP97">
+            <v>4.8699812692597009</v>
+          </cell>
+          <cell r="BQ97">
+            <v>20.859493256001233</v>
+          </cell>
+          <cell r="BR97">
+            <v>8.0426911288215255</v>
+          </cell>
+          <cell r="BS97">
+            <v>4.1822389372623281</v>
+          </cell>
+          <cell r="BT97">
+            <v>6.7710432008686903</v>
+          </cell>
+          <cell r="BU97">
+            <v>26.209024554975635</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="BM116">
+            <v>8.2228986546205558</v>
+          </cell>
+          <cell r="BN116">
+            <v>1.0104755651357047</v>
+          </cell>
+          <cell r="BO116">
+            <v>1.0635868807786328</v>
+          </cell>
+          <cell r="BP116">
+            <v>8.9609572144490883</v>
+          </cell>
+          <cell r="BQ116">
+            <v>12.100729048226007</v>
+          </cell>
+          <cell r="BR116">
+            <v>26.451775486787799</v>
+          </cell>
+          <cell r="BS116">
+            <v>26.425974432654776</v>
+          </cell>
+          <cell r="BT116">
+            <v>10.761599243689275</v>
+          </cell>
+          <cell r="BU116">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="BM135">
+            <v>4.0246364451652639</v>
+          </cell>
+          <cell r="BN135">
+            <v>2.2178035992971914</v>
+          </cell>
+          <cell r="BO135">
+            <v>10.442780191250822</v>
+          </cell>
+          <cell r="BP135">
+            <v>3.0168753156801063</v>
+          </cell>
+          <cell r="BQ135">
+            <v>18.740877943436466</v>
+          </cell>
+          <cell r="BR135">
+            <v>1.0677211323407854</v>
+          </cell>
+          <cell r="BS135">
+            <v>41.491048826065843</v>
+          </cell>
+          <cell r="BT135">
+            <v>1.5206394431597063</v>
+          </cell>
+          <cell r="BU135">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="BM154">
+            <v>7.5118698993463502</v>
+          </cell>
+          <cell r="BN154">
+            <v>0.47971667978146237</v>
+          </cell>
+          <cell r="BO154">
+            <v>2.577938250719841</v>
+          </cell>
+          <cell r="BP154">
+            <v>25.059588584565812</v>
+          </cell>
+          <cell r="BQ154">
+            <v>7.283225884355188</v>
+          </cell>
+          <cell r="BR154">
+            <v>11.480273866940198</v>
+          </cell>
+          <cell r="BS154">
+            <v>15.610706231166374</v>
+          </cell>
+          <cell r="BT154">
+            <v>11.508253303697305</v>
+          </cell>
+          <cell r="BU154">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="BM173">
+            <v>59.103001414794655</v>
+          </cell>
+          <cell r="BN173">
+            <v>0.50691244239631339</v>
+          </cell>
+          <cell r="BO173">
+            <v>0</v>
+          </cell>
+          <cell r="BP173">
+            <v>3.1762656932205888</v>
+          </cell>
+          <cell r="BQ173">
+            <v>8.5689544262329456</v>
+          </cell>
+          <cell r="BR173">
+            <v>8.7256866096993964</v>
+          </cell>
+          <cell r="BS173">
+            <v>31.434657036442747</v>
+          </cell>
+          <cell r="BT173">
+            <v>9.81412982052702</v>
+          </cell>
+          <cell r="BU173">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="BM192">
+            <v>6.640568143636469</v>
+          </cell>
+          <cell r="BN192">
+            <v>0.40723966233655384</v>
+          </cell>
+          <cell r="BO192">
+            <v>18.647303978264375</v>
+          </cell>
+          <cell r="BP192">
+            <v>8.4442076582985504</v>
+          </cell>
+          <cell r="BQ192">
+            <v>9.9362432150602853</v>
+          </cell>
+          <cell r="BR192">
+            <v>47.701335003384315</v>
+          </cell>
+          <cell r="BS192">
+            <v>26.076203140711002</v>
+          </cell>
+          <cell r="BT192">
+            <v>3.7383898616248699</v>
+          </cell>
+          <cell r="BU192">
+            <v>8.309618550856527</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="BM211">
+            <v>6.4571840254064758</v>
+          </cell>
+          <cell r="BN211">
+            <v>4.6869779511358942</v>
+          </cell>
+          <cell r="BO211">
+            <v>2.4952562952907202</v>
+          </cell>
+          <cell r="BP211">
+            <v>15.373617727978653</v>
+          </cell>
+          <cell r="BQ211">
+            <v>21.677612600318135</v>
+          </cell>
+          <cell r="BR211">
+            <v>5.3175607443009794</v>
+          </cell>
+          <cell r="BS211">
+            <v>24.729064412469807</v>
+          </cell>
+          <cell r="BT211">
+            <v>2.4873161832720427</v>
+          </cell>
+          <cell r="BU211">
+            <v>2.979629864170882</v>
+          </cell>
+        </row>
+        <row r="230">
+          <cell r="BM230">
+            <v>4.5842156854696148</v>
+          </cell>
+          <cell r="BN230">
+            <v>0.95145621289964843</v>
+          </cell>
+          <cell r="BO230">
+            <v>8.2336566557987538</v>
+          </cell>
+          <cell r="BP230">
+            <v>38.814775182315877</v>
+          </cell>
+          <cell r="BQ230">
+            <v>33.417434428107569</v>
+          </cell>
+          <cell r="BR230">
+            <v>12.381410690553825</v>
+          </cell>
+          <cell r="BS230">
+            <v>48.24458570746237</v>
+          </cell>
+          <cell r="BT230">
+            <v>11.984357710892249</v>
+          </cell>
+          <cell r="BU230">
+            <v>23.353207910254277</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,102 +843,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED475CF7-10EB-4BDC-9A06-7D1F7405D9FF}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>-1.1000000000000001</v>
-      </c>
-      <c r="C2">
-        <v>-1.43</v>
-      </c>
-      <c r="D2">
-        <v>-2.89</v>
-      </c>
-      <c r="E2">
-        <v>-1.89</v>
-      </c>
-      <c r="F2">
-        <v>-3.23</v>
-      </c>
-      <c r="G2">
-        <v>-0.5</v>
-      </c>
-      <c r="H2">
-        <v>-2.9</v>
-      </c>
-      <c r="I2">
-        <v>-1.32</v>
-      </c>
-      <c r="J2">
-        <v>-0.61</v>
+      <c r="B2" s="3">
+        <f>-[1]Sheet4!BM$78</f>
+        <v>-1.6723376794962399</v>
+      </c>
+      <c r="C2" s="3">
+        <f>-[1]Sheet4!BN$78</f>
+        <v>-1.9196079004924875</v>
+      </c>
+      <c r="D2" s="3">
+        <f>-[1]Sheet4!BO$78</f>
+        <v>-2.7558985848572726</v>
+      </c>
+      <c r="E2" s="3">
+        <f>-[1]Sheet4!BP$78</f>
+        <v>-0.1604641310330728</v>
+      </c>
+      <c r="F2" s="3">
+        <f>-[1]Sheet4!BQ$78</f>
+        <v>-4.1152896617819481</v>
+      </c>
+      <c r="G2" s="3">
+        <f>-[1]Sheet4!BR$78</f>
+        <v>-0.32415605702635442</v>
+      </c>
+      <c r="H2" s="3">
+        <f>-[1]Sheet4!BS$78</f>
+        <v>-5.2871023596143258</v>
+      </c>
+      <c r="I2" s="3">
+        <f>-[1]Sheet4!BT$78</f>
+        <v>-0.4551162969937726</v>
+      </c>
+      <c r="J2" s="3">
+        <f>-[1]Sheet4!BU$78</f>
+        <v>-4.3082198150677886</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>-1.1599999999999999</v>
-      </c>
-      <c r="C3">
-        <v>-0.62</v>
-      </c>
-      <c r="D3">
-        <v>-4.95</v>
-      </c>
-      <c r="E3">
-        <v>-1.81</v>
-      </c>
-      <c r="F3">
-        <v>-5.12</v>
-      </c>
-      <c r="G3">
-        <v>-0.46</v>
-      </c>
-      <c r="H3">
-        <v>-14.23</v>
-      </c>
-      <c r="I3">
-        <v>-0.76</v>
-      </c>
-      <c r="J3">
+      <c r="B3" s="3">
+        <f>-[1]Sheet4!BM$135</f>
+        <v>-4.0246364451652639</v>
+      </c>
+      <c r="C3" s="3">
+        <f>-[1]Sheet4!BN$135</f>
+        <v>-2.2178035992971914</v>
+      </c>
+      <c r="D3" s="3">
+        <f>-[1]Sheet4!BO$135</f>
+        <v>-10.442780191250822</v>
+      </c>
+      <c r="E3" s="3">
+        <f>-[1]Sheet4!BP$135</f>
+        <v>-3.0168753156801063</v>
+      </c>
+      <c r="F3" s="3">
+        <f>-[1]Sheet4!BQ$135</f>
+        <v>-18.740877943436466</v>
+      </c>
+      <c r="G3" s="3">
+        <f>-[1]Sheet4!BR$135</f>
+        <v>-1.0677211323407854</v>
+      </c>
+      <c r="H3" s="3">
+        <f>-[1]Sheet4!BS$135</f>
+        <v>-41.491048826065843</v>
+      </c>
+      <c r="I3" s="3">
+        <f>-[1]Sheet4!BT$135</f>
+        <v>-1.5206394431597063</v>
+      </c>
+      <c r="J3" s="3">
+        <f>-[1]Sheet4!BU$135</f>
         <v>0</v>
       </c>
     </row>
@@ -585,288 +968,410 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>-0.6</v>
-      </c>
-      <c r="C4">
-        <v>-5.4</v>
-      </c>
-      <c r="D4">
-        <v>-2.09</v>
-      </c>
-      <c r="E4">
-        <v>-1.08</v>
-      </c>
-      <c r="F4">
-        <v>-1.08</v>
-      </c>
-      <c r="G4">
-        <v>-0.92</v>
-      </c>
-      <c r="H4">
-        <v>-2</v>
-      </c>
-      <c r="I4">
-        <v>-0.81</v>
-      </c>
-      <c r="J4">
-        <v>-0.93</v>
+      <c r="B4" s="3">
+        <f>-[1]Sheet4!BM$21</f>
+        <v>-3.2592816165294627</v>
+      </c>
+      <c r="C4" s="3">
+        <f>-[1]Sheet4!BN$21</f>
+        <v>-10.33368572011617</v>
+      </c>
+      <c r="D4" s="3">
+        <f>-[1]Sheet4!BO$21</f>
+        <v>-22.394819271147433</v>
+      </c>
+      <c r="E4" s="3">
+        <f>-[1]Sheet4!BP$21</f>
+        <v>-3.5330811594172671</v>
+      </c>
+      <c r="F4" s="3">
+        <f>-[1]Sheet4!BQ$21</f>
+        <v>-2.0125972621416643</v>
+      </c>
+      <c r="G4" s="3">
+        <f>-[1]Sheet4!BR$21</f>
+        <v>-4.4628622369061421</v>
+      </c>
+      <c r="H4" s="3">
+        <f>-[1]Sheet4!BS$21</f>
+        <v>-1.6687258339981561</v>
+      </c>
+      <c r="I4" s="3">
+        <f>-[1]Sheet4!BT$21</f>
+        <v>-2.7598774804851423</v>
+      </c>
+      <c r="J4" s="3">
+        <f>-[1]Sheet4!BU$21</f>
+        <v>-1.0050811425673827</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>-2.44</v>
-      </c>
-      <c r="C5">
-        <v>-2.88</v>
-      </c>
-      <c r="D5">
-        <v>-15.81</v>
-      </c>
-      <c r="E5">
-        <v>-7.14</v>
-      </c>
-      <c r="F5">
-        <v>-4.32</v>
-      </c>
-      <c r="G5">
-        <v>-3.41</v>
-      </c>
-      <c r="H5">
-        <v>-6.57</v>
-      </c>
-      <c r="I5">
-        <v>-5.03</v>
-      </c>
-      <c r="J5">
-        <v>-4.13</v>
+      <c r="B5" s="3">
+        <f>-[1]Sheet4!BM$59</f>
+        <v>-12.649951689465617</v>
+      </c>
+      <c r="C5" s="3">
+        <f>-[1]Sheet4!BN$59</f>
+        <v>-2.576452136380186</v>
+      </c>
+      <c r="D5" s="3">
+        <f>-[1]Sheet4!BO$59</f>
+        <v>-28.273817766748337</v>
+      </c>
+      <c r="E5" s="3">
+        <f>-[1]Sheet4!BP$59</f>
+        <v>-11.385096173096438</v>
+      </c>
+      <c r="F5" s="3">
+        <f>-[1]Sheet4!BQ$59</f>
+        <v>-13.405632030785759</v>
+      </c>
+      <c r="G5" s="3">
+        <f>-[1]Sheet4!BR$59</f>
+        <v>-8.534651666069939</v>
+      </c>
+      <c r="H5" s="3">
+        <f>-[1]Sheet4!BS$59</f>
+        <v>-36.361072353619136</v>
+      </c>
+      <c r="I5" s="3">
+        <f>-[1]Sheet4!BT$59</f>
+        <v>-5.1946086854736313</v>
+      </c>
+      <c r="J5" s="3">
+        <f>-[1]Sheet4!BU$59</f>
+        <v>-30.704496097842831</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>-2.83</v>
-      </c>
-      <c r="C6">
-        <v>-1.61</v>
-      </c>
-      <c r="D6">
-        <v>-5.34</v>
-      </c>
-      <c r="E6">
-        <v>-5.45</v>
-      </c>
-      <c r="F6">
-        <v>-7.91</v>
-      </c>
-      <c r="G6">
-        <v>-2.54</v>
-      </c>
-      <c r="H6">
-        <v>-2.4</v>
-      </c>
-      <c r="I6">
-        <v>-5</v>
-      </c>
-      <c r="J6">
-        <v>-5.96</v>
+      <c r="B6" s="3">
+        <f>-[1]Sheet4!BM$97</f>
+        <v>-5.8083733799160093</v>
+      </c>
+      <c r="C6" s="3">
+        <f>-[1]Sheet4!BN$97</f>
+        <v>-1.8673556284186359</v>
+      </c>
+      <c r="D6" s="3">
+        <f>-[1]Sheet4!BO$97</f>
+        <v>-6.5249602147018653</v>
+      </c>
+      <c r="E6" s="3">
+        <f>-[1]Sheet4!BP$97</f>
+        <v>-4.8699812692597009</v>
+      </c>
+      <c r="F6" s="3">
+        <f>-[1]Sheet4!BQ$97</f>
+        <v>-20.859493256001233</v>
+      </c>
+      <c r="G6" s="3">
+        <f>-[1]Sheet4!BR$97</f>
+        <v>-8.0426911288215255</v>
+      </c>
+      <c r="H6" s="3">
+        <f>-[1]Sheet4!BS$97</f>
+        <v>-4.1822389372623281</v>
+      </c>
+      <c r="I6" s="3">
+        <f>-[1]Sheet4!BT$97</f>
+        <v>-6.7710432008686903</v>
+      </c>
+      <c r="J6" s="3">
+        <f>-[1]Sheet4!BU$97</f>
+        <v>-26.209024554975635</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>-0.83</v>
-      </c>
-      <c r="C7">
-        <v>-1.58</v>
-      </c>
-      <c r="D7">
-        <v>-10.15</v>
-      </c>
-      <c r="E7">
-        <v>-2.88</v>
-      </c>
-      <c r="F7">
-        <v>-1.47</v>
-      </c>
-      <c r="G7">
-        <v>-6.71</v>
-      </c>
-      <c r="H7">
-        <v>-0.85</v>
-      </c>
-      <c r="I7">
-        <v>-4.72</v>
-      </c>
-      <c r="J7">
-        <v>-0.67</v>
+        <v>20</v>
+      </c>
+      <c r="B7" s="3">
+        <f>-[1]Sheet4!BM$21</f>
+        <v>-3.2592816165294627</v>
+      </c>
+      <c r="C7" s="3">
+        <f>-[1]Sheet4!BN$21</f>
+        <v>-10.33368572011617</v>
+      </c>
+      <c r="D7" s="3">
+        <f>-[1]Sheet4!BO$21</f>
+        <v>-22.394819271147433</v>
+      </c>
+      <c r="E7" s="3">
+        <f>-[1]Sheet4!BP$21</f>
+        <v>-3.5330811594172671</v>
+      </c>
+      <c r="F7" s="3">
+        <f>-[1]Sheet4!BQ$21</f>
+        <v>-2.0125972621416643</v>
+      </c>
+      <c r="G7" s="3">
+        <f>-[1]Sheet4!BR$21</f>
+        <v>-4.4628622369061421</v>
+      </c>
+      <c r="H7" s="3">
+        <f>-[1]Sheet4!BS$21</f>
+        <v>-1.6687258339981561</v>
+      </c>
+      <c r="I7" s="3">
+        <f>-[1]Sheet4!BT$21</f>
+        <v>-2.7598774804851423</v>
+      </c>
+      <c r="J7" s="3">
+        <f>-[1]Sheet4!BU$21</f>
+        <v>-1.0050811425673827</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>-2.5499999999999998</v>
-      </c>
-      <c r="C8">
-        <v>-2.2400000000000002</v>
-      </c>
-      <c r="D8">
-        <v>-4.4800000000000004</v>
-      </c>
-      <c r="E8">
-        <v>-6.66</v>
-      </c>
-      <c r="F8">
-        <v>-6.2</v>
-      </c>
-      <c r="G8">
-        <v>-6.51</v>
-      </c>
-      <c r="H8">
-        <v>-9.19</v>
-      </c>
-      <c r="I8">
-        <v>-6.19</v>
-      </c>
-      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <f>-[1]Sheet4!BM$116</f>
+        <v>-8.2228986546205558</v>
+      </c>
+      <c r="C8" s="3">
+        <f>-[1]Sheet4!BN$116</f>
+        <v>-1.0104755651357047</v>
+      </c>
+      <c r="D8" s="3">
+        <f>-[1]Sheet4!BO$116</f>
+        <v>-1.0635868807786328</v>
+      </c>
+      <c r="E8" s="3">
+        <f>-[1]Sheet4!BP$116</f>
+        <v>-8.9609572144490883</v>
+      </c>
+      <c r="F8" s="3">
+        <f>-[1]Sheet4!BQ$116</f>
+        <v>-12.100729048226007</v>
+      </c>
+      <c r="G8" s="3">
+        <f>-[1]Sheet4!BR$116</f>
+        <v>-26.451775486787799</v>
+      </c>
+      <c r="H8" s="3">
+        <f>-[1]Sheet4!BS$116</f>
+        <v>-26.425974432654776</v>
+      </c>
+      <c r="I8" s="3">
+        <f>-[1]Sheet4!BT$116</f>
+        <v>-10.761599243689275</v>
+      </c>
+      <c r="J8" s="3">
+        <f>-[1]Sheet4!BU$116</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>-11.51</v>
-      </c>
-      <c r="C9">
-        <v>-6.97</v>
-      </c>
-      <c r="D9">
-        <v>-11.89</v>
-      </c>
-      <c r="E9">
-        <v>-24.36</v>
-      </c>
-      <c r="F9">
-        <v>-14.18</v>
-      </c>
-      <c r="G9">
-        <v>-10.3</v>
-      </c>
-      <c r="H9">
-        <v>-18.649999999999999</v>
-      </c>
-      <c r="I9">
-        <v>-21.32</v>
-      </c>
-      <c r="J9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <f>-[1]Sheet4!BM$154</f>
+        <v>-7.5118698993463502</v>
+      </c>
+      <c r="C9" s="3">
+        <f>-[1]Sheet4!BN$154</f>
+        <v>-0.47971667978146237</v>
+      </c>
+      <c r="D9" s="3">
+        <f>-[1]Sheet4!BO$154</f>
+        <v>-2.577938250719841</v>
+      </c>
+      <c r="E9" s="3">
+        <f>-[1]Sheet4!BP$154</f>
+        <v>-25.059588584565812</v>
+      </c>
+      <c r="F9" s="3">
+        <f>-[1]Sheet4!BQ$154</f>
+        <v>-7.283225884355188</v>
+      </c>
+      <c r="G9" s="3">
+        <f>-[1]Sheet4!BR$154</f>
+        <v>-11.480273866940198</v>
+      </c>
+      <c r="H9" s="3">
+        <f>-[1]Sheet4!BS$154</f>
+        <v>-15.610706231166374</v>
+      </c>
+      <c r="I9" s="3">
+        <f>-[1]Sheet4!BT$154</f>
+        <v>-11.508253303697305</v>
+      </c>
+      <c r="J9" s="3">
+        <f>-[1]Sheet4!BU$154</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>-25.53</v>
-      </c>
-      <c r="C10">
-        <v>-0.8</v>
-      </c>
-      <c r="D10">
-        <v>-6.94</v>
-      </c>
-      <c r="E10">
-        <v>-0.91</v>
-      </c>
-      <c r="F10">
-        <v>-2.21</v>
-      </c>
-      <c r="G10">
-        <v>-1.95</v>
-      </c>
-      <c r="H10">
-        <v>-8.1199999999999992</v>
-      </c>
-      <c r="I10">
-        <v>-4.28</v>
-      </c>
-      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <f>-[1]Sheet4!BM$173</f>
+        <v>-59.103001414794655</v>
+      </c>
+      <c r="C10" s="3">
+        <f>-[1]Sheet4!BN$173</f>
+        <v>-0.50691244239631339</v>
+      </c>
+      <c r="D10" s="3">
+        <f>-[1]Sheet4!BO$173</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f>-[1]Sheet4!BP$173</f>
+        <v>-3.1762656932205888</v>
+      </c>
+      <c r="F10" s="3">
+        <f>-[1]Sheet4!BQ$173</f>
+        <v>-8.5689544262329456</v>
+      </c>
+      <c r="G10" s="3">
+        <f>-[1]Sheet4!BR$173</f>
+        <v>-8.7256866096993964</v>
+      </c>
+      <c r="H10" s="3">
+        <f>-[1]Sheet4!BS$173</f>
+        <v>-31.434657036442747</v>
+      </c>
+      <c r="I10" s="3">
+        <f>-[1]Sheet4!BT$173</f>
+        <v>-9.81412982052702</v>
+      </c>
+      <c r="J10" s="3">
+        <f>-[1]Sheet4!BU$173</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>-3.98</v>
-      </c>
-      <c r="C11">
-        <v>-1.3</v>
-      </c>
-      <c r="D11">
-        <v>-19.22</v>
-      </c>
-      <c r="E11">
-        <v>-6.48</v>
-      </c>
-      <c r="F11">
-        <v>-6.16</v>
-      </c>
-      <c r="G11">
-        <v>-18.21</v>
-      </c>
-      <c r="H11">
-        <v>-15.87</v>
-      </c>
-      <c r="I11">
-        <v>-4.1399999999999997</v>
-      </c>
-      <c r="J11">
-        <v>-5.46</v>
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <f>-[1]Sheet4!BM$192</f>
+        <v>-6.640568143636469</v>
+      </c>
+      <c r="C11" s="3">
+        <f>-[1]Sheet4!BN$192</f>
+        <v>-0.40723966233655384</v>
+      </c>
+      <c r="D11" s="3">
+        <f>-[1]Sheet4!BO$192</f>
+        <v>-18.647303978264375</v>
+      </c>
+      <c r="E11" s="3">
+        <f>-[1]Sheet4!BP$192</f>
+        <v>-8.4442076582985504</v>
+      </c>
+      <c r="F11" s="3">
+        <f>-[1]Sheet4!BQ$192</f>
+        <v>-9.9362432150602853</v>
+      </c>
+      <c r="G11" s="3">
+        <f>-[1]Sheet4!BR$192</f>
+        <v>-47.701335003384315</v>
+      </c>
+      <c r="H11" s="3">
+        <f>-[1]Sheet4!BS$192</f>
+        <v>-26.076203140711002</v>
+      </c>
+      <c r="I11" s="3">
+        <f>-[1]Sheet4!BT$192</f>
+        <v>-3.7383898616248699</v>
+      </c>
+      <c r="J11" s="3">
+        <f>-[1]Sheet4!BU$192</f>
+        <v>-8.309618550856527</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>-4.45</v>
-      </c>
-      <c r="C12">
-        <v>-5.73</v>
-      </c>
-      <c r="D12">
-        <v>-8.1300000000000008</v>
-      </c>
-      <c r="E12">
-        <v>-13.7</v>
-      </c>
-      <c r="F12">
-        <v>-23.93</v>
-      </c>
-      <c r="G12">
-        <v>-4.9800000000000004</v>
-      </c>
-      <c r="H12">
-        <v>-23.75</v>
-      </c>
-      <c r="I12">
-        <v>-7.48</v>
-      </c>
-      <c r="J12">
-        <v>-3.23</v>
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <f>-[1]Sheet4!BM$211</f>
+        <v>-6.4571840254064758</v>
+      </c>
+      <c r="C12" s="3">
+        <f>-[1]Sheet4!BN$211</f>
+        <v>-4.6869779511358942</v>
+      </c>
+      <c r="D12" s="3">
+        <f>-[1]Sheet4!BO$211</f>
+        <v>-2.4952562952907202</v>
+      </c>
+      <c r="E12" s="3">
+        <f>-[1]Sheet4!BP$211</f>
+        <v>-15.373617727978653</v>
+      </c>
+      <c r="F12" s="3">
+        <f>-[1]Sheet4!BQ$211</f>
+        <v>-21.677612600318135</v>
+      </c>
+      <c r="G12" s="3">
+        <f>-[1]Sheet4!BR$211</f>
+        <v>-5.3175607443009794</v>
+      </c>
+      <c r="H12" s="3">
+        <f>-[1]Sheet4!BS$211</f>
+        <v>-24.729064412469807</v>
+      </c>
+      <c r="I12" s="3">
+        <f>-[1]Sheet4!BT$211</f>
+        <v>-2.4873161832720427</v>
+      </c>
+      <c r="J12" s="3">
+        <f>-[1]Sheet4!BU$211</f>
+        <v>-2.979629864170882</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3">
+        <f>-[1]Sheet4!BM$230</f>
+        <v>-4.5842156854696148</v>
+      </c>
+      <c r="C13" s="3">
+        <f>-[1]Sheet4!BN$230</f>
+        <v>-0.95145621289964843</v>
+      </c>
+      <c r="D13" s="3">
+        <f>-[1]Sheet4!BO$230</f>
+        <v>-8.2336566557987538</v>
+      </c>
+      <c r="E13" s="3">
+        <f>-[1]Sheet4!BP$230</f>
+        <v>-38.814775182315877</v>
+      </c>
+      <c r="F13" s="3">
+        <f>-[1]Sheet4!BQ$230</f>
+        <v>-33.417434428107569</v>
+      </c>
+      <c r="G13" s="3">
+        <f>-[1]Sheet4!BR$230</f>
+        <v>-12.381410690553825</v>
+      </c>
+      <c r="H13" s="3">
+        <f>-[1]Sheet4!BS$230</f>
+        <v>-48.24458570746237</v>
+      </c>
+      <c r="I13" s="3">
+        <f>-[1]Sheet4!BT$230</f>
+        <v>-11.984357710892249</v>
+      </c>
+      <c r="J13" s="3">
+        <f>-[1]Sheet4!BU$230</f>
+        <v>-23.353207910254277</v>
       </c>
     </row>
   </sheetData>
